--- a/ClosedXML.Tests/Resource/Other/NumberFormats/NonSequentialNumberFormatsIds-Input.xlsx
+++ b/ClosedXML.Tests/Resource/Other/NumberFormats/NonSequentialNumberFormatsIds-Input.xlsx
@@ -90,8 +90,8 @@
   </x:cellStyleXfs>
   <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/ClosedXML.Tests/Resource/Other/NumberFormats/NonSequentialNumberFormatsIds-Input.xlsx
+++ b/ClosedXML.Tests/Resource/Other/NumberFormats/NonSequentialNumberFormatsIds-Input.xlsx
@@ -90,8 +90,8 @@
   </x:cellStyleXfs>
   <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="2"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
